--- a/output/pdf_financials_xlsx/GBML.xlsx
+++ b/output/pdf_financials_xlsx/GBML.xlsx
@@ -1020,34 +1020,34 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.036793</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.025454</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.013163</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.011792</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.005404</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.001537</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.002012</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.012737</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.01662</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.01379</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1935,34 +1935,34 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.133343</v>
+        <v>-1.170136</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.40669</v>
+        <v>-1.432144</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.8221850000000001</v>
+        <v>-0.835348</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.922963</v>
+        <v>-0.934755</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.428303</v>
+        <v>-0.433707</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.481734</v>
+        <v>-0.483271</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.610612</v>
+        <v>-0.6126239999999999</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.745412</v>
+        <v>-0.758149</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.439088</v>
+        <v>-1.455708</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.741168</v>
+        <v>-0.754958</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-2.002164</v>
@@ -2049,34 +2049,34 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.133343</v>
+        <v>-1.170136</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.40669</v>
+        <v>-1.432144</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.8221850000000001</v>
+        <v>-0.835348</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.922963</v>
+        <v>-0.934755</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.428303</v>
+        <v>-0.433707</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.481734</v>
+        <v>-0.483271</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.610612</v>
+        <v>-0.6126239999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.745412</v>
+        <v>-0.758149</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.439088</v>
+        <v>-1.455708</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.741168</v>
+        <v>-0.754958</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-2.002164</v>
@@ -2339,52 +2339,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>5.353944</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.552751</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.217302</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.4874</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.856948</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.432545</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.07736999999999999</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.224689</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.545257</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.748243</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.753905</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.67457</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.418253</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.072528</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.425785</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.752244</v>
       </c>
     </row>
     <row r="35">
@@ -2449,52 +2449,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>5.353944</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.552751</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.217302</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.4874</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.856948</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.432545</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.07736999999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.224689</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.545257</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.748243</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.753905</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>2.67457</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.418253</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.072528</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.425785</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.752244</v>
       </c>
     </row>
     <row r="37">
@@ -3109,52 +3109,52 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>5.373681</v>
+        <v>0.019737</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.600956</v>
+        <v>0.048205</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.233927</v>
+        <v>0.016625</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.506832</v>
+        <v>0.019432</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.87414</v>
+        <v>0.017192</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.442374</v>
+        <v>0.009828999999999999</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.094766</v>
+        <v>0.017396</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.234377</v>
+        <v>0.009688</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.610215</v>
+        <v>0.064958</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.824366</v>
+        <v>0.076123</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.766278</v>
+        <v>0.012373</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.736991</v>
+        <v>0.062421</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.478162</v>
+        <v>0.059909</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.089428</v>
+        <v>0.0169</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.475783</v>
+        <v>0.049998</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.793444</v>
+        <v>0.0412</v>
       </c>
     </row>
     <row r="49">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -25346,7 +25346,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -41264,7 +41264,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
